--- a/Modelo_G_J.xlsx
+++ b/Modelo_G_J.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmgaia-my.sharepoint.com/personal/marco_cm-gaia_pt/Documents/Ambiente de Trabalho/Scripts Py/IRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{0E0A7546-2C5D-431D-964D-91E8C98773F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92587C3C-8F9D-4708-8C34-632D72686DE0}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{0E0A7546-2C5D-431D-964D-91E8C98773F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18C761E2-1500-4E4E-86D6-07EA2B78A8EA}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-600" windowWidth="29040" windowHeight="15720" xr2:uid="{5AF578CE-57BC-4E85-B768-16B5ACA05C37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{5AF578CE-57BC-4E85-B768-16B5ACA05C37}"/>
   </bookViews>
   <sheets>
     <sheet name="G01" sheetId="1" r:id="rId1"/>
+    <sheet name="Trading212" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="161">
   <si>
     <t>DataR</t>
   </si>
@@ -72,13 +73,463 @@
   </si>
   <si>
     <t>Imposto</t>
+  </si>
+  <si>
+    <t>Linha</t>
+  </si>
+  <si>
+    <t>Realização (Data)</t>
+  </si>
+  <si>
+    <t>Aquisição (Data)</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>País Fonte</t>
+  </si>
+  <si>
+    <t>Cód.</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Trade Republic</t>
+  </si>
+  <si>
+    <t>TL0</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>Iberdrola</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices</t>
+  </si>
+  <si>
+    <t>Johnson &amp; Johnson</t>
+  </si>
+  <si>
+    <t>SoundHound AI</t>
+  </si>
+  <si>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum</t>
+  </si>
+  <si>
+    <t>ALTR</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>PTX</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Super Micro Computer</t>
+  </si>
+  <si>
+    <t>NKE</t>
+  </si>
+  <si>
+    <t>Meta Platforms</t>
+  </si>
+  <si>
+    <t>SoFi Technologies</t>
+  </si>
+  <si>
+    <t>ACHR</t>
+  </si>
+  <si>
+    <t>HIMS</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers Health</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>TRMLF</t>
+  </si>
+  <si>
+    <t>HNST</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>Energy Fuels</t>
+  </si>
+  <si>
+    <t>Valor Realiz. (€)</t>
+  </si>
+  <si>
+    <t>Valor Aquisiç. (€)</t>
+  </si>
+  <si>
+    <t>Mob. Negoc.</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>04.02.2025</t>
+  </si>
+  <si>
+    <t>US69608A1088</t>
+  </si>
+  <si>
+    <t>24.02.2025</t>
+  </si>
+  <si>
+    <t>US86800U3023</t>
+  </si>
+  <si>
+    <t>25.03.2025</t>
+  </si>
+  <si>
+    <t>US0213691035</t>
+  </si>
+  <si>
+    <t>27.08.2025</t>
+  </si>
+  <si>
+    <t>US7561091049</t>
+  </si>
+  <si>
+    <t>07.10.2025</t>
+  </si>
+  <si>
+    <t>US88160R1014</t>
+  </si>
+  <si>
+    <t>04.11.2025</t>
+  </si>
+  <si>
+    <t>US26740W1099</t>
+  </si>
+  <si>
+    <t>06.11.2025</t>
+  </si>
+  <si>
+    <t>US81730H1095</t>
+  </si>
+  <si>
+    <t>07.11.2025</t>
+  </si>
+  <si>
+    <t>US6541061031</t>
+  </si>
+  <si>
+    <t>24.11.2025</t>
+  </si>
+  <si>
+    <t>CA89156V1067</t>
+  </si>
+  <si>
+    <t>30.12.2025</t>
+  </si>
+  <si>
+    <t>US03945R1023</t>
+  </si>
+  <si>
+    <t>US4383331067</t>
+  </si>
+  <si>
+    <t>US4330001060</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
+  </si>
+  <si>
+    <t>Coluna2</t>
+  </si>
+  <si>
+    <t>Coluna3</t>
+  </si>
+  <si>
+    <t>Coluna4</t>
+  </si>
+  <si>
+    <t>Coluna5</t>
+  </si>
+  <si>
+    <t>Coluna6</t>
+  </si>
+  <si>
+    <t>Coluna7</t>
+  </si>
+  <si>
+    <t>Coluna8</t>
+  </si>
+  <si>
+    <t>Coluna9</t>
+  </si>
+  <si>
+    <t>Coluna10</t>
+  </si>
+  <si>
+    <t>Coluna11</t>
+  </si>
+  <si>
+    <t>Data Execução</t>
+  </si>
+  <si>
+    <t>Instrumento</t>
+  </si>
+  <si>
+    <t>Qtd. (Tamanho)</t>
+  </si>
+  <si>
+    <t>Preço Execução (EUR)</t>
+  </si>
+  <si>
+    <t>Valor Realização (EUR)</t>
+  </si>
+  <si>
+    <t>840 (EUA)</t>
+  </si>
+  <si>
+    <t>124 (CAN)</t>
+  </si>
+  <si>
+    <t>3.295,24</t>
+  </si>
+  <si>
+    <t>Preço Médio (€)</t>
+  </si>
+  <si>
+    <t>Preço de Mercado (€)</t>
+  </si>
+  <si>
+    <t>Resultado Total (EUR)</t>
+  </si>
+  <si>
+    <t>US0079031078</t>
+  </si>
+  <si>
+    <t>US0231351067</t>
+  </si>
+  <si>
+    <t>CA2926717083</t>
+  </si>
+  <si>
+    <t>ES0144580Y14</t>
+  </si>
+  <si>
+    <t>US4781601046</t>
+  </si>
+  <si>
+    <t>US30303M1027</t>
+  </si>
+  <si>
+    <t>US5949181045</t>
+  </si>
+  <si>
+    <t>US67066G1040</t>
+  </si>
+  <si>
+    <t>US70450Y1038</t>
+  </si>
+  <si>
+    <t>US83406F1021</t>
+  </si>
+  <si>
+    <t>US8361001071</t>
+  </si>
+  <si>
+    <t>iShares Gold ETC</t>
+  </si>
+  <si>
+    <t>IE0009JOT9U1</t>
+  </si>
+  <si>
+    <t>Ativos a 31.12.2025</t>
+  </si>
+  <si>
+    <t>Vendas ocorridas entre 31.12.2024 e 31.12.2025</t>
+  </si>
+  <si>
+    <t>Ativo (Ticker)</t>
+  </si>
+  <si>
+    <t>10.01.2025</t>
+  </si>
+  <si>
+    <t>20.12.2024</t>
+  </si>
+  <si>
+    <t>02.01.2025</t>
+  </si>
+  <si>
+    <t>09.01.2025</t>
+  </si>
+  <si>
+    <t>05.02.2025</t>
+  </si>
+  <si>
+    <t>15.01.2025</t>
+  </si>
+  <si>
+    <t>15.05.2025</t>
+  </si>
+  <si>
+    <t>12.06.2025</t>
+  </si>
+  <si>
+    <t>22.07.2025</t>
+  </si>
+  <si>
+    <t>10.04.2025</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>Palantir (PTX)</t>
+  </si>
+  <si>
+    <t>Super Micro (SMCI)</t>
+  </si>
+  <si>
+    <t>Altair (ALTR)</t>
+  </si>
+  <si>
+    <t>D-Wave (QBTS)</t>
+  </si>
+  <si>
+    <t>SentinelOne (S)</t>
+  </si>
+  <si>
+    <t>Nike (NKE)</t>
+  </si>
+  <si>
+    <t>Archer (ACHR)</t>
+  </si>
+  <si>
+    <t>Honest Co (HNST)</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers (HIMS)</t>
+  </si>
+  <si>
+    <t>Contraparte</t>
+  </si>
+  <si>
+    <t>Realty Inc (O)</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Lote 1</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Lote 2</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Lote 3</t>
+  </si>
+  <si>
+    <t>Tourmaline - Lote 1</t>
+  </si>
+  <si>
+    <t>Tourmaline - Lote 2</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>Contrap.</t>
+  </si>
+  <si>
+    <t>Mob. Neg.</t>
+  </si>
+  <si>
+    <t>SentinelOne (S) - L1</t>
+  </si>
+  <si>
+    <t>SentinelOne (S) - L2</t>
+  </si>
+  <si>
+    <t>Nike (NKE) - L1</t>
+  </si>
+  <si>
+    <t>Nike (NKE) - L2</t>
+  </si>
+  <si>
+    <t>Nike (NKE) - L3</t>
+  </si>
+  <si>
+    <t>Archer (ACHR) - L1</t>
+  </si>
+  <si>
+    <t>Archer (ACHR) - L2</t>
+  </si>
+  <si>
+    <t>Archer (ACHR) - L3</t>
+  </si>
+  <si>
+    <t>Honest Co (HNST) - L1</t>
+  </si>
+  <si>
+    <t>Honest Co (HNST) - L2</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers (HIMS)-L1</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers (HIMS)-L2</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers (HIMS)-L3</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers (HIMS)-L4</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Venda 1 L1</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Venda 1 L2</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Venda 1 L3</t>
+  </si>
+  <si>
+    <t>Tesla (TL0) - Venda 2</t>
+  </si>
+  <si>
+    <t>TRMLF - Venda 1</t>
+  </si>
+  <si>
+    <t>TRMLF - Venda 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -89,6 +540,18 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -108,18 +571,262 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{41C4037C-688C-4018-A564-FA271FCFFF2C}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="24">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -252,9 +959,9 @@
     <sortCondition ref="A1:A31"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{19341CEC-B2F8-4D9F-8512-942A2630383D}" name="DataR" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{19341CEC-B2F8-4D9F-8512-942A2630383D}" name="DataR" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{55D371B2-9A1C-470D-93FC-570711070785}" name="ValorR"/>
-    <tableColumn id="3" xr3:uid="{416C83EF-4866-4AA1-9C0D-A78F05F34FE9}" name="DataA" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{416C83EF-4866-4AA1-9C0D-A78F05F34FE9}" name="DataA" dataDxfId="22"/>
     <tableColumn id="4" xr3:uid="{D1D2786D-AC18-49C7-BC2D-93A815F6F0F1}" name="ValorA"/>
     <tableColumn id="5" xr3:uid="{1BF99B9E-4C06-446B-ACA6-5B7C2B034299}" name="Despesas"/>
   </tableColumns>
@@ -263,13 +970,101 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F8A39F2E-E2A1-4658-9694-1039EA782D1B}" name="Tabela2" displayName="Tabela2" ref="G1:J4" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F8A39F2E-E2A1-4658-9694-1039EA782D1B}" name="Tabela2" displayName="Tabela2" ref="G1:J4" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="G1:J4" xr:uid="{F8A39F2E-E2A1-4658-9694-1039EA782D1B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{54AD5850-6CCC-4BB4-A98A-6E6D5A5318DE}" name="Código" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{A7446D5E-7D33-4D6C-AF4E-6331A82131B1}" name="PaisFonte" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{152BFAA2-39CD-4A0F-B769-BD70D486E635}" name="RBruto" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{58DC6BEA-2A27-41D5-B369-8BA4C54CED60}" name="Imposto" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{54AD5850-6CCC-4BB4-A98A-6E6D5A5318DE}" name="Código" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A7446D5E-7D33-4D6C-AF4E-6331A82131B1}" name="PaisFonte" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{152BFAA2-39CD-4A0F-B769-BD70D486E635}" name="RBruto" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{58DC6BEA-2A27-41D5-B369-8BA4C54CED60}" name="Imposto" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E60ABB26-DC22-4AAE-A071-94C5CFDF240F}" name="Tabela3" displayName="Tabela3" ref="L4:V24" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4">
+  <autoFilter ref="L4:V24" xr:uid="{E60ABB26-DC22-4AAE-A071-94C5CFDF240F}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{13CAAB7B-1725-49FE-8EEE-B6328976601A}" name="Coluna1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{6CC03971-025F-4481-A84D-9D00F84E5D18}" name="Coluna2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{098D6991-9A62-40A0-AF50-BF2B0D1C0581}" name="Coluna3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{C3491262-C5AA-457C-8B29-75694F9F82F6}" name="Coluna4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{23BA2D52-E2FE-41E1-9227-B69CE2C849E1}" name="Coluna5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{08707985-198B-46DC-966B-6B59ACAC46D2}" name="Coluna6" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{0BA1CE45-A1CD-4130-A2CA-86E5C19C25F9}" name="Coluna7" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{73ECA4B8-010D-4613-9539-33498323CC5C}" name="Coluna8" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{981B844C-51FF-4EFB-8470-B29B25933634}" name="Coluna9" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{0965E7B2-D0A6-40F6-BA72-926FBB9012F3}" name="Coluna10" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D0021D4C-098C-4C76-8DB1-054BCB9DB2EB}" name="Coluna11" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9D82DC3E-6122-4B8F-9606-D0E1793A1B9D}" name="Tabela4" displayName="Tabela4" ref="A2:F17" totalsRowShown="0">
+  <autoFilter ref="A2:F17" xr:uid="{9D82DC3E-6122-4B8F-9606-D0E1793A1B9D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{A9FF6953-DC6A-4CC3-A155-E31B8C24D89F}" name="Instrumento"/>
+    <tableColumn id="2" xr3:uid="{BA717EE7-BEA4-4F25-81B0-DBAB4419555B}" name="ISIN"/>
+    <tableColumn id="3" xr3:uid="{433EAA16-FA18-4CF0-940F-6B4EE7348827}" name="Qtd. (Tamanho)"/>
+    <tableColumn id="4" xr3:uid="{35AE4C16-8733-4BDB-B78D-2D5E29FA5661}" name="Preço Médio (€)"/>
+    <tableColumn id="5" xr3:uid="{A1D310A5-EB31-48CE-A146-8E3FC99249C3}" name="Preço de Mercado (€)"/>
+    <tableColumn id="6" xr3:uid="{AEECDEC9-B980-4D11-9F20-144FC3D313D6}" name="Resultado Total (EUR)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{48792A5D-C9BF-4DC6-8BAE-4DBD28DF7939}" name="Tabela6" displayName="Tabela6" ref="A20:G34" totalsRowShown="0">
+  <autoFilter ref="A20:G34" xr:uid="{48792A5D-C9BF-4DC6-8BAE-4DBD28DF7939}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{0978A767-B52E-4938-A010-B453A827C585}" name="Data Execução"/>
+    <tableColumn id="2" xr3:uid="{B0BFFE71-DBEE-4E77-91F0-ECDDECDC0986}" name="Instrumento"/>
+    <tableColumn id="3" xr3:uid="{56428013-2198-40E5-B2D4-6E5BC8210603}" name="ISIN"/>
+    <tableColumn id="4" xr3:uid="{AA32B05C-6BFC-4043-823D-70B55169C328}" name="Qtd. (Tamanho)"/>
+    <tableColumn id="5" xr3:uid="{9D056771-26CC-41FB-B6FF-1464B89EB23F}" name="Preço Execução (EUR)"/>
+    <tableColumn id="6" xr3:uid="{10EAC073-2ADA-4B21-B34B-41065AE5137F}" name="Valor Realização (EUR)"/>
+    <tableColumn id="7" xr3:uid="{48D2C245-49A0-4AE2-BDC6-A6637B1FDE73}" name="País Fonte"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{37369C51-388F-4C55-A31B-83B756CEB9DF}" name="Tabela10" displayName="Tabela10" ref="A37:I52" totalsRowShown="0">
+  <autoFilter ref="A37:I52" xr:uid="{37369C51-388F-4C55-A31B-83B756CEB9DF}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A93BB9CE-7465-4493-AB27-1C38FB6DBF42}" name="Ativo"/>
+    <tableColumn id="2" xr3:uid="{82A94FAD-B20C-4210-8BD1-189D456C5568}" name="País Fonte"/>
+    <tableColumn id="3" xr3:uid="{716A70F9-C057-41A9-8DE3-C1A964DFE700}" name="Cód."/>
+    <tableColumn id="4" xr3:uid="{42BC71C1-D386-450B-BD54-5574986928FC}" name="Realização (Data)" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{53264EA9-AFAA-4C7F-AA10-5A73BFA82643}" name="Valor Realiz. (€)"/>
+    <tableColumn id="6" xr3:uid="{3781E6CC-2C26-458F-B2DD-BA6678AD6646}" name="Aquisição (Data)"/>
+    <tableColumn id="7" xr3:uid="{1924711A-4CDC-408B-AEBE-41690962AF7F}" name="Valor Aquisiç. (€)"/>
+    <tableColumn id="8" xr3:uid="{0724CACC-194C-4ADB-94C7-13D45BDAEBB3}" name="Contraparte"/>
+    <tableColumn id="9" xr3:uid="{B8E549B4-227E-47A5-9582-4C7A9E041097}" name="Mob. Negoc."/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{74924605-725E-4321-B6BD-0117D7BCB054}" name="Tabela12" displayName="Tabela12" ref="A55:J80" totalsRowShown="0">
+  <autoFilter ref="A55:J80" xr:uid="{74924605-725E-4321-B6BD-0117D7BCB054}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{40D6CB78-A8BB-4FA4-9016-92330974E146}" name="Linha"/>
+    <tableColumn id="2" xr3:uid="{76047A3B-4903-42BC-97C7-C258B7622CC4}" name="Ativo (Ticker)"/>
+    <tableColumn id="3" xr3:uid="{1614FA56-335B-4A11-B3B0-5E6F32C2B711}" name="País"/>
+    <tableColumn id="4" xr3:uid="{D13602C2-5851-4807-A2A9-87AEE3C28A26}" name="Cód."/>
+    <tableColumn id="5" xr3:uid="{A4CCB3ED-BE4B-408E-B7D4-0182EBE84877}" name="Realização (Data)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{3A4BF70D-E497-4857-8CC3-F33121A0B07D}" name="Valor Realiz. (€)"/>
+    <tableColumn id="7" xr3:uid="{F9505335-F866-4221-BB72-670A269CE492}" name="Aquisição (Data)" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{1C01DD91-E969-4D5B-A793-C12C2BDA89A0}" name="Valor Aquisiç. (€)"/>
+    <tableColumn id="9" xr3:uid="{26E8637D-978D-435C-AE50-589B741FFF02}" name="Contrap."/>
+    <tableColumn id="10" xr3:uid="{9FA7DB2E-0CA2-4314-880E-A90C9759DFA8}" name="Mob. Neg."/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -562,7 +1357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0E2AC6-82CA-486B-9424-34BCAF61E336}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -570,15 +1365,23 @@
     <col min="3" max="3" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" style="2" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="11" width="3.140625" style="2" customWidth="1"/>
+    <col min="12" max="14" width="10.28515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="10.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.28515625" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +1410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -633,7 +1436,7 @@
         <v>5.2138999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -658,8 +1461,21 @@
       <c r="J3" s="2">
         <v>2.8140000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -684,8 +1500,41 @@
       <c r="J4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -698,8 +1547,41 @@
       <c r="D5" s="2">
         <v>3.94</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L5" s="2">
+        <v>951</v>
+      </c>
+      <c r="M5" s="2">
+        <v>208</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="1">
+        <v>45677</v>
+      </c>
+      <c r="P5" s="2">
+        <v>74.72</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>45649</v>
+      </c>
+      <c r="R5" s="2">
+        <v>85.7</v>
+      </c>
+      <c r="S5" s="2">
+        <v>2</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>276</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -712,8 +1594,41 @@
       <c r="D6" s="2">
         <v>3.97</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L6" s="2">
+        <v>952</v>
+      </c>
+      <c r="M6" s="2">
+        <v>376</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="1">
+        <v>45951</v>
+      </c>
+      <c r="P6" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>45659</v>
+      </c>
+      <c r="R6" s="2">
+        <v>48.2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>2</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>276</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -726,8 +1641,41 @@
       <c r="D7" s="2">
         <v>3.96</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L7" s="2">
+        <v>953</v>
+      </c>
+      <c r="M7" s="2">
+        <v>840</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="1">
+        <v>45779</v>
+      </c>
+      <c r="P7" s="2">
+        <v>296.61</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>45665</v>
+      </c>
+      <c r="R7" s="2">
+        <v>194.97</v>
+      </c>
+      <c r="S7" s="2">
+        <v>2</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>276</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -740,8 +1688,41 @@
       <c r="D8" s="2">
         <v>3.95</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L8" s="2">
+        <v>954</v>
+      </c>
+      <c r="M8" s="2">
+        <v>840</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" s="1">
+        <v>45951</v>
+      </c>
+      <c r="P8" s="2">
+        <v>58.27</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>45649</v>
+      </c>
+      <c r="R8" s="2">
+        <v>74.55</v>
+      </c>
+      <c r="S8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>276</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -754,8 +1735,41 @@
       <c r="D9" s="2">
         <v>7.92</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L9" s="2">
+        <v>955</v>
+      </c>
+      <c r="M9" s="2">
+        <v>840</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" s="1">
+        <v>45951</v>
+      </c>
+      <c r="P9" s="2">
+        <v>58.27</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>45677</v>
+      </c>
+      <c r="R9" s="2">
+        <v>69.260000000000005</v>
+      </c>
+      <c r="S9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>276</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -768,8 +1782,41 @@
       <c r="D10" s="2">
         <v>19.79</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L10" s="2">
+        <v>956</v>
+      </c>
+      <c r="M10" s="2">
+        <v>840</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="1">
+        <v>45694</v>
+      </c>
+      <c r="P10" s="2">
+        <v>110</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>45670</v>
+      </c>
+      <c r="R10" s="2">
+        <v>121</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>276</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -782,8 +1829,41 @@
       <c r="D11" s="2">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L11" s="2">
+        <v>957</v>
+      </c>
+      <c r="M11" s="2">
+        <v>840</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" s="1">
+        <v>45712</v>
+      </c>
+      <c r="P11" s="2">
+        <v>259.89999999999998</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>45672</v>
+      </c>
+      <c r="R11" s="2">
+        <v>150</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>276</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -796,8 +1876,41 @@
       <c r="D12" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L12" s="2">
+        <v>958</v>
+      </c>
+      <c r="M12" s="2">
+        <v>840</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O12" s="1">
+        <v>45712</v>
+      </c>
+      <c r="P12" s="2">
+        <v>259.89999999999998</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>45685</v>
+      </c>
+      <c r="R12" s="2">
+        <v>134.94999999999999</v>
+      </c>
+      <c r="S12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>276</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -810,8 +1923,41 @@
       <c r="D13" s="2">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L13" s="2">
+        <v>959</v>
+      </c>
+      <c r="M13" s="2">
+        <v>840</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O13" s="1">
+        <v>45985</v>
+      </c>
+      <c r="P13" s="2">
+        <v>54.69</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>45692</v>
+      </c>
+      <c r="R13" s="2">
+        <v>63.71</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>276</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -824,8 +1970,41 @@
       <c r="D14" s="2">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L14" s="2">
+        <v>960</v>
+      </c>
+      <c r="M14" s="2">
+        <v>840</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" s="1">
+        <v>45985</v>
+      </c>
+      <c r="P14" s="2">
+        <v>588.72</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>45692</v>
+      </c>
+      <c r="R14" s="2">
+        <v>685.8</v>
+      </c>
+      <c r="S14" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>276</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -838,8 +2017,41 @@
       <c r="D15" s="2">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L15" s="2">
+        <v>961</v>
+      </c>
+      <c r="M15" s="2">
+        <v>840</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O15" s="1">
+        <v>45985</v>
+      </c>
+      <c r="P15" s="2">
+        <v>34.22</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>45693</v>
+      </c>
+      <c r="R15" s="2">
+        <v>40.1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>276</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -852,8 +2064,41 @@
       <c r="D16" s="2">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L16" s="2">
+        <v>962</v>
+      </c>
+      <c r="M16" s="2">
+        <v>840</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O16" s="1">
+        <v>45985</v>
+      </c>
+      <c r="P16" s="2">
+        <v>303.57</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>45693</v>
+      </c>
+      <c r="R16" s="2">
+        <v>355.72</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>276</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -866,8 +2111,41 @@
       <c r="D17" s="2">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L17" s="2">
+        <v>963</v>
+      </c>
+      <c r="M17" s="2">
+        <v>840</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O17" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P17" s="2">
+        <v>157.5</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>45653</v>
+      </c>
+      <c r="R17" s="2">
+        <v>118.02</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1.29</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>276</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -880,8 +2158,41 @@
       <c r="D18" s="2">
         <v>2.64</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L18" s="2">
+        <v>964</v>
+      </c>
+      <c r="M18" s="2">
+        <v>840</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O18" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P18" s="2">
+        <v>393.75</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>45754</v>
+      </c>
+      <c r="R18" s="2">
+        <v>281.85000000000002</v>
+      </c>
+      <c r="S18" s="2">
+        <v>1.71</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>276</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -894,8 +2205,41 @@
       <c r="D19" s="2">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L19" s="2">
+        <v>965</v>
+      </c>
+      <c r="M19" s="2">
+        <v>840</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O19" s="1">
+        <v>45782</v>
+      </c>
+      <c r="P19" s="2">
+        <v>421.73</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>45769</v>
+      </c>
+      <c r="R19" s="2">
+        <v>347.2</v>
+      </c>
+      <c r="S19" s="2">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>276</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45708.377916666701</v>
       </c>
@@ -908,8 +2252,41 @@
       <c r="D20" s="2">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L20" s="2">
+        <v>966</v>
+      </c>
+      <c r="M20" s="2">
+        <v>840</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O20" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P20" s="2">
+        <v>5.56</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>44873</v>
+      </c>
+      <c r="R20" s="2">
+        <v>3</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>276</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45708.377920659703</v>
       </c>
@@ -922,8 +2299,41 @@
       <c r="D21" s="2">
         <v>19.93</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L21" s="2">
+        <v>967</v>
+      </c>
+      <c r="M21" s="2">
+        <v>840</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O21" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P21" s="2">
+        <v>32.18</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>44875</v>
+      </c>
+      <c r="R21" s="2">
+        <v>18</v>
+      </c>
+      <c r="S21" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>276</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45708.377920659703</v>
       </c>
@@ -936,8 +2346,41 @@
       <c r="D22" s="2">
         <v>9.89</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L22" s="2">
+        <v>968</v>
+      </c>
+      <c r="M22" s="2">
+        <v>840</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P22" s="2">
+        <v>28.45</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>44876</v>
+      </c>
+      <c r="R22" s="2">
+        <v>16</v>
+      </c>
+      <c r="S22" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>276</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45708.377920659703</v>
       </c>
@@ -950,8 +2393,41 @@
       <c r="D23" s="2">
         <v>3.05</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L23" s="2">
+        <v>969</v>
+      </c>
+      <c r="M23" s="2">
+        <v>840</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O23" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P23" s="2">
+        <v>7.27</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>44882</v>
+      </c>
+      <c r="R23" s="2">
+        <v>4</v>
+      </c>
+      <c r="S23" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>276</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45726.766274363399</v>
       </c>
@@ -964,8 +2440,41 @@
       <c r="D24" s="2">
         <v>4.57</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L24" s="2">
+        <v>970</v>
+      </c>
+      <c r="M24" s="2">
+        <v>840</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="1">
+        <v>45838</v>
+      </c>
+      <c r="P24" s="2">
+        <v>349.75</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>45733</v>
+      </c>
+      <c r="R24" s="2">
+        <v>292.64</v>
+      </c>
+      <c r="S24" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <v>276</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45726.766274374997</v>
       </c>
@@ -979,7 +2488,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45769.488319687502</v>
       </c>
@@ -993,7 +2502,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45947.757846574103</v>
       </c>
@@ -1006,8 +2515,31 @@
       <c r="D27" s="2">
         <v>39.32</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45947.757846574103</v>
       </c>
@@ -1020,8 +2552,31 @@
       <c r="D28" s="2">
         <v>36.799999999999997</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O28" s="7">
+        <v>2</v>
+      </c>
+      <c r="P28" s="2">
+        <v>100.04</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>200.08</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45978.645854872702</v>
       </c>
@@ -1034,8 +2589,31 @@
       <c r="D29" s="2">
         <v>213.68</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O29" s="7">
+        <v>2</v>
+      </c>
+      <c r="P29" s="2">
+        <v>51.49</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>102.98</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45978.646062361098</v>
       </c>
@@ -1048,8 +2626,31 @@
       <c r="D30" s="2">
         <v>80.78</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="L30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O30" s="7">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2">
+        <v>104.68</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>104.68</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45978.691863634303</v>
       </c>
@@ -1062,12 +2663,2378 @@
       <c r="D31" s="2">
         <v>71.47</v>
       </c>
+      <c r="L31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0.179394</v>
+      </c>
+      <c r="P31" s="2">
+        <v>50.28</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>9.02</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="L32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O32" s="7">
+        <v>1.0091346000000001</v>
+      </c>
+      <c r="P32" s="2">
+        <v>388.95</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>392.5</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+    </row>
+    <row r="33" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O33" s="7">
+        <v>10</v>
+      </c>
+      <c r="P33" s="2">
+        <v>27.65</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>276.5</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+    </row>
+    <row r="34" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O34" s="7">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2">
+        <v>400.05</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>400.05</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" s="7">
+        <v>15</v>
+      </c>
+      <c r="P35" s="2">
+        <v>14.27</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>214.05</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+    </row>
+    <row r="36" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" s="7">
+        <v>4</v>
+      </c>
+      <c r="P36" s="2">
+        <v>53.68</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>214.72</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+    </row>
+    <row r="37" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O37" s="7">
+        <v>5.6950000000000003</v>
+      </c>
+      <c r="P37" s="2">
+        <v>38.6</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>219.83</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O38" s="7">
+        <v>4.3049999999999997</v>
+      </c>
+      <c r="P38" s="2">
+        <v>38.590000000000003</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>166.13</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O39" s="7">
+        <v>35</v>
+      </c>
+      <c r="P39" s="2">
+        <v>6.59</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>230.65</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O40" s="7">
+        <v>100</v>
+      </c>
+      <c r="P40" s="2">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>228</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+    </row>
+    <row r="41" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O41" s="7">
+        <v>15</v>
+      </c>
+      <c r="P41" s="2">
+        <v>29.07</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>436.05</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+    </row>
+    <row r="42" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+    </row>
+    <row r="43" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+    </row>
+    <row r="44" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+    </row>
+    <row r="45" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O45" s="1"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+    </row>
+    <row r="46" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+    </row>
+    <row r="47" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+    </row>
+    <row r="48" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="O48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+    </row>
+    <row r="49" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+    </row>
+    <row r="50" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+    </row>
+    <row r="51" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+    </row>
+    <row r="52" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+    </row>
+    <row r="53" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L3:V3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EDCE334-F839-4520-AF03-DE80B3C2CDA0}">
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>110.08</v>
+      </c>
+      <c r="E3">
+        <v>184.12</v>
+      </c>
+      <c r="F3">
+        <v>814.39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>186.7</v>
+      </c>
+      <c r="E4">
+        <v>197.18</v>
+      </c>
+      <c r="F4">
+        <v>73.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>5.89</v>
+      </c>
+      <c r="E5">
+        <v>26.26</v>
+      </c>
+      <c r="F5">
+        <v>166.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14.24</v>
+      </c>
+      <c r="E6">
+        <v>14.55</v>
+      </c>
+      <c r="F6">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>40.07</v>
+      </c>
+      <c r="E7">
+        <v>32.43</v>
+      </c>
+      <c r="F7">
+        <v>-111.93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8">
+        <v>4.1732979700000001</v>
+      </c>
+      <c r="D8">
+        <v>12.36</v>
+      </c>
+      <c r="E8">
+        <v>18.465</v>
+      </c>
+      <c r="F8">
+        <v>25.46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>136.77000000000001</v>
+      </c>
+      <c r="E9">
+        <v>176.7</v>
+      </c>
+      <c r="F9">
+        <v>39.93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>3.15</v>
+      </c>
+      <c r="D10">
+        <v>577.05999999999995</v>
+      </c>
+      <c r="E10">
+        <v>659.66</v>
+      </c>
+      <c r="F10">
+        <v>163.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>365.24</v>
+      </c>
+      <c r="E11">
+        <v>413.3</v>
+      </c>
+      <c r="F11">
+        <v>96.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>117.29</v>
+      </c>
+      <c r="E12">
+        <v>160.34</v>
+      </c>
+      <c r="F12">
+        <v>258.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>56.07</v>
+      </c>
+      <c r="E13">
+        <v>50.68</v>
+      </c>
+      <c r="F13">
+        <v>-97.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>14.85</v>
+      </c>
+      <c r="E14">
+        <v>26.12</v>
+      </c>
+      <c r="F14">
+        <v>221.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>12.22</v>
+      </c>
+      <c r="E15">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="F15">
+        <v>-104.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>40.51</v>
+      </c>
+      <c r="E16">
+        <v>29.2</v>
+      </c>
+      <c r="F16">
+        <v>-355.51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>47.46</v>
+      </c>
+      <c r="E17">
+        <v>77.775000000000006</v>
+      </c>
+      <c r="F17">
+        <v>30.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>100.04</v>
+      </c>
+      <c r="F21">
+        <v>200.08</v>
+      </c>
+      <c r="G21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>51.49</v>
+      </c>
+      <c r="F22">
+        <v>102.98</v>
+      </c>
+      <c r="G22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>104.68</v>
+      </c>
+      <c r="F23">
+        <v>104.68</v>
+      </c>
+      <c r="G23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24">
+        <v>0.179394</v>
+      </c>
+      <c r="E24">
+        <v>50.28</v>
+      </c>
+      <c r="F24">
+        <v>9.02</v>
+      </c>
+      <c r="G24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25">
+        <v>1.0091346000000001</v>
+      </c>
+      <c r="E25">
+        <v>388.95</v>
+      </c>
+      <c r="F25">
+        <v>392.5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>27.65</v>
+      </c>
+      <c r="F26">
+        <v>276.5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>400.05</v>
+      </c>
+      <c r="F27">
+        <v>400.05</v>
+      </c>
+      <c r="G27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+      <c r="E28">
+        <v>14.27</v>
+      </c>
+      <c r="F28">
+        <v>214.05</v>
+      </c>
+      <c r="G28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>53.68</v>
+      </c>
+      <c r="F29">
+        <v>214.72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30">
+        <v>5.6950000000000003</v>
+      </c>
+      <c r="E30">
+        <v>38.6</v>
+      </c>
+      <c r="F30">
+        <v>219.83</v>
+      </c>
+      <c r="G30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31">
+        <v>4.3049999999999997</v>
+      </c>
+      <c r="E31">
+        <v>38.590000000000003</v>
+      </c>
+      <c r="F31">
+        <v>166.13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>35</v>
+      </c>
+      <c r="E32">
+        <v>6.59</v>
+      </c>
+      <c r="F32">
+        <v>230.65</v>
+      </c>
+      <c r="G32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F33">
+        <v>228</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34">
+        <v>15</v>
+      </c>
+      <c r="E34">
+        <v>29.07</v>
+      </c>
+      <c r="F34">
+        <v>436.05</v>
+      </c>
+      <c r="G34" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38">
+        <v>840</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="3">
+        <v>45692</v>
+      </c>
+      <c r="E38">
+        <v>100.04</v>
+      </c>
+      <c r="F38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38">
+        <v>128.97999999999999</v>
+      </c>
+      <c r="H38">
+        <v>196</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39">
+        <v>840</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="3">
+        <v>45712</v>
+      </c>
+      <c r="E39">
+        <v>51.49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39">
+        <v>57</v>
+      </c>
+      <c r="H39">
+        <v>196</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40">
+        <v>840</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="3">
+        <v>45741</v>
+      </c>
+      <c r="E40">
+        <v>104.68</v>
+      </c>
+      <c r="F40" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40">
+        <v>103.73</v>
+      </c>
+      <c r="H40">
+        <v>196</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41">
+        <v>840</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3">
+        <v>45896</v>
+      </c>
+      <c r="E41">
+        <v>9.02</v>
+      </c>
+      <c r="F41" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="H41">
+        <v>196</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42">
+        <v>840</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="3">
+        <v>45937</v>
+      </c>
+      <c r="E42">
+        <v>304.93</v>
+      </c>
+      <c r="F42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42">
+        <v>237.42</v>
+      </c>
+      <c r="H42">
+        <v>196</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43">
+        <v>840</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="3">
+        <v>45937</v>
+      </c>
+      <c r="E43">
+        <v>87.57</v>
+      </c>
+      <c r="F43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43">
+        <v>64.739999999999995</v>
+      </c>
+      <c r="H43">
+        <v>196</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44">
+        <v>840</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="3">
+        <v>45965</v>
+      </c>
+      <c r="E44">
+        <v>27.65</v>
+      </c>
+      <c r="F44" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44">
+        <v>5.89</v>
+      </c>
+      <c r="H44">
+        <v>196</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45">
+        <v>840</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="3">
+        <v>45965</v>
+      </c>
+      <c r="E45">
+        <v>400.05</v>
+      </c>
+      <c r="F45" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45">
+        <v>302.16000000000003</v>
+      </c>
+      <c r="H45">
+        <v>196</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46">
+        <v>840</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E46">
+        <v>14.27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46">
+        <v>19.13</v>
+      </c>
+      <c r="H46">
+        <v>196</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47">
+        <v>840</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="3">
+        <v>45968</v>
+      </c>
+      <c r="E47">
+        <v>53.68</v>
+      </c>
+      <c r="F47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G47">
+        <v>65.709999999999994</v>
+      </c>
+      <c r="H47">
+        <v>196</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48">
+        <v>124</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="3">
+        <v>45985</v>
+      </c>
+      <c r="E48">
+        <v>38.6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48">
+        <v>35.01</v>
+      </c>
+      <c r="H48">
+        <v>196</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49">
+        <v>124</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="3">
+        <v>45985</v>
+      </c>
+      <c r="E49">
+        <v>38.590000000000003</v>
+      </c>
+      <c r="F49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49">
+        <v>29.78</v>
+      </c>
+      <c r="H49">
+        <v>196</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50">
+        <v>840</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="3">
+        <v>46021</v>
+      </c>
+      <c r="E50">
+        <v>6.59</v>
+      </c>
+      <c r="F50" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50">
+        <v>10.64</v>
+      </c>
+      <c r="H50">
+        <v>196</v>
+      </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51">
+        <v>840</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="3">
+        <v>46021</v>
+      </c>
+      <c r="E51">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F51" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51">
+        <v>3.96</v>
+      </c>
+      <c r="H51">
+        <v>196</v>
+      </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52">
+        <v>840</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3">
+        <v>46021</v>
+      </c>
+      <c r="E52">
+        <v>29.07</v>
+      </c>
+      <c r="F52" t="s">
+        <v>119</v>
+      </c>
+      <c r="G52">
+        <v>40.07</v>
+      </c>
+      <c r="H52">
+        <v>196</v>
+      </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" t="s">
+        <v>139</v>
+      </c>
+      <c r="J55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>840</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="3">
+        <v>45692</v>
+      </c>
+      <c r="F56">
+        <v>200.08</v>
+      </c>
+      <c r="G56" s="3">
+        <v>45667</v>
+      </c>
+      <c r="H56">
+        <v>128.97999999999999</v>
+      </c>
+      <c r="I56">
+        <v>196</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>840</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="3">
+        <v>45712</v>
+      </c>
+      <c r="F57">
+        <v>102.98</v>
+      </c>
+      <c r="G57" s="3">
+        <v>45707</v>
+      </c>
+      <c r="H57">
+        <v>109.37</v>
+      </c>
+      <c r="I57">
+        <v>196</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>840</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="3">
+        <v>45741</v>
+      </c>
+      <c r="F58">
+        <v>104.68</v>
+      </c>
+      <c r="G58" s="3">
+        <v>45646</v>
+      </c>
+      <c r="H58">
+        <v>103.73</v>
+      </c>
+      <c r="I58">
+        <v>196</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59">
+        <v>840</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="3">
+        <v>45896</v>
+      </c>
+      <c r="F59">
+        <v>9.02</v>
+      </c>
+      <c r="G59" s="3">
+        <v>45646</v>
+      </c>
+      <c r="H59">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="I59">
+        <v>196</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60">
+        <v>840</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="3">
+        <v>45937</v>
+      </c>
+      <c r="F60">
+        <v>185.42</v>
+      </c>
+      <c r="G60" s="3">
+        <v>45646</v>
+      </c>
+      <c r="H60">
+        <v>192.33</v>
+      </c>
+      <c r="I60">
+        <v>196</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61">
+        <v>840</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="3">
+        <v>45937</v>
+      </c>
+      <c r="F61">
+        <v>16.48</v>
+      </c>
+      <c r="G61" s="3">
+        <v>45659</v>
+      </c>
+      <c r="H61">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="I61">
+        <v>196</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62">
+        <v>840</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="3">
+        <v>45937</v>
+      </c>
+      <c r="F62">
+        <v>190.6</v>
+      </c>
+      <c r="G62" s="3">
+        <v>45700</v>
+      </c>
+      <c r="H62">
+        <v>158.56</v>
+      </c>
+      <c r="I62">
+        <v>196</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>8</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63">
+        <v>840</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="3">
+        <v>45965</v>
+      </c>
+      <c r="F63">
+        <v>276.55</v>
+      </c>
+      <c r="G63" s="3">
+        <v>45646</v>
+      </c>
+      <c r="H63">
+        <v>56.72</v>
+      </c>
+      <c r="I63">
+        <v>196</v>
+      </c>
+      <c r="J63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>9</v>
+      </c>
+      <c r="B64" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64">
+        <v>840</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="3">
+        <v>45965</v>
+      </c>
+      <c r="F64">
+        <v>400.05</v>
+      </c>
+      <c r="G64" s="3">
+        <v>45740</v>
+      </c>
+      <c r="H64">
+        <v>239.35</v>
+      </c>
+      <c r="I64">
+        <v>196</v>
+      </c>
+      <c r="J64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65">
+        <v>840</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F65">
+        <v>142.72</v>
+      </c>
+      <c r="G65" s="3">
+        <v>45866</v>
+      </c>
+      <c r="H65">
+        <v>170.63</v>
+      </c>
+      <c r="I65">
+        <v>196</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66">
+        <v>840</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F66">
+        <v>71.36</v>
+      </c>
+      <c r="G66" s="3">
+        <v>45870</v>
+      </c>
+      <c r="H66">
+        <v>77.19</v>
+      </c>
+      <c r="I66">
+        <v>196</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67">
+        <v>840</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="3">
+        <v>45968</v>
+      </c>
+      <c r="F67">
+        <v>53.68</v>
+      </c>
+      <c r="G67" s="3">
+        <v>45712</v>
+      </c>
+      <c r="H67">
+        <v>76.33</v>
+      </c>
+      <c r="I67">
+        <v>196</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68">
+        <v>840</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="3">
+        <v>45968</v>
+      </c>
+      <c r="F68">
+        <v>53.68</v>
+      </c>
+      <c r="G68" s="3">
+        <v>45740</v>
+      </c>
+      <c r="H68">
+        <v>63.26</v>
+      </c>
+      <c r="I68">
+        <v>196</v>
+      </c>
+      <c r="J68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69">
+        <v>840</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="3">
+        <v>45968</v>
+      </c>
+      <c r="F69">
+        <v>107.36</v>
+      </c>
+      <c r="G69" s="3">
+        <v>45919</v>
+      </c>
+      <c r="H69">
+        <v>123.28</v>
+      </c>
+      <c r="I69">
+        <v>196</v>
+      </c>
+      <c r="J69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70">
+        <v>124</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="3">
+        <v>45985</v>
+      </c>
+      <c r="F70">
+        <v>219.8</v>
+      </c>
+      <c r="G70" s="3">
+        <v>45911</v>
+      </c>
+      <c r="H70">
+        <v>208.14</v>
+      </c>
+      <c r="I70">
+        <v>196</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>16</v>
+      </c>
+      <c r="B71" t="s">
+        <v>160</v>
+      </c>
+      <c r="C71">
+        <v>124</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="3">
+        <v>45985</v>
+      </c>
+      <c r="F71">
+        <v>166.15</v>
+      </c>
+      <c r="G71" s="3">
+        <v>45911</v>
+      </c>
+      <c r="H71">
+        <v>157.34</v>
+      </c>
+      <c r="I71">
+        <v>196</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>17</v>
+      </c>
+      <c r="B72" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72">
+        <v>840</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F72">
+        <v>131.75</v>
+      </c>
+      <c r="G72" s="3">
+        <v>45796</v>
+      </c>
+      <c r="H72">
+        <v>200.81</v>
+      </c>
+      <c r="I72">
+        <v>196</v>
+      </c>
+      <c r="J72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>18</v>
+      </c>
+      <c r="B73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73">
+        <v>840</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F73">
+        <v>65.88</v>
+      </c>
+      <c r="G73" s="3">
+        <v>45918</v>
+      </c>
+      <c r="H73">
+        <v>76.38</v>
+      </c>
+      <c r="I73">
+        <v>196</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74">
+        <v>840</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F74">
+        <v>32.94</v>
+      </c>
+      <c r="G74" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H74">
+        <v>48.75</v>
+      </c>
+      <c r="I74">
+        <v>196</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>20</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75">
+        <v>840</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F75">
+        <v>182.34</v>
+      </c>
+      <c r="G75" s="3">
+        <v>45911</v>
+      </c>
+      <c r="H75">
+        <v>269.3</v>
+      </c>
+      <c r="I75">
+        <v>196</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76">
+        <v>840</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F76">
+        <v>45.58</v>
+      </c>
+      <c r="G76" s="3">
+        <v>45936</v>
+      </c>
+      <c r="H76">
+        <v>67.97</v>
+      </c>
+      <c r="I76">
+        <v>196</v>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>22</v>
+      </c>
+      <c r="B77" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77">
+        <v>840</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F77">
+        <v>290.70999999999998</v>
+      </c>
+      <c r="G77" s="3">
+        <v>45831</v>
+      </c>
+      <c r="H77">
+        <v>368.96</v>
+      </c>
+      <c r="I77">
+        <v>196</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78">
+        <v>840</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F78">
+        <v>58.14</v>
+      </c>
+      <c r="G78" s="3">
+        <v>45936</v>
+      </c>
+      <c r="H78">
+        <v>92.19</v>
+      </c>
+      <c r="I78">
+        <v>196</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>24</v>
+      </c>
+      <c r="B79" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79">
+        <v>840</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F79">
+        <v>58.14</v>
+      </c>
+      <c r="G79" s="3">
+        <v>45964</v>
+      </c>
+      <c r="H79">
+        <v>82.39</v>
+      </c>
+      <c r="I79">
+        <v>196</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80">
+        <v>840</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="3">
+        <v>46021</v>
+      </c>
+      <c r="F80">
+        <v>29.07</v>
+      </c>
+      <c r="G80" s="3">
+        <v>45968</v>
+      </c>
+      <c r="H80">
+        <v>35.43</v>
+      </c>
+      <c r="I80">
+        <v>196</v>
+      </c>
+      <c r="J80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>